--- a/questionnaire/sources.xlsx
+++ b/questionnaire/sources.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831"/>
+    <workbookView xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Figures" sheetId="1" r:id="rId1"/>
@@ -8314,7 +8314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6862" uniqueCount="2328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8514" uniqueCount="2329">
   <si>
     <t>Country</t>
   </si>
@@ -15319,6 +15319,9 @@
   </si>
   <si>
     <t>RMB 250</t>
+  </si>
+  <si>
+    <t>Pour quelle liste avez-vous vot&amp;eacute; aux &lt;span id="election"&gt;&amp;eacute;lections europ&amp;eacute;ennes de 2024&lt;/span&gt; ?</t>
   </si>
 </sst>
 </file>
@@ -68265,7 +68268,7 @@
         <v>1637</v>
       </c>
       <c r="B98" s="39" t="s">
-        <v>1435</v>
+        <v>2328</v>
       </c>
       <c r="C98" s="39" t="s">
         <v>1618</v>
